--- a/checklist_forms/050_refrigerated_trailer_scheduled_maintenance_checklist--checklist_forms.xlsx
+++ b/checklist_forms/050_refrigerated_trailer_scheduled_maintenance_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'trailer'}</t>
+          <t>trailer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Trailer'}</t>
+          <t>Trailer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'tractor'}</t>
+          <t>tractor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Tractor'}</t>
+          <t>Tractor</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'generator'}</t>
+          <t>generator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Generator'}</t>
+          <t>Generator</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'5k'}</t>
+          <t>5k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '5k'}</t>
+          <t>5k</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'10k'}</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '10k'}</t>
+          <t>10k</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'20k'}</t>
+          <t>20k</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '20k'}</t>
+          <t>20k</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'dirty'}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Dirty'}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'50-60'}</t>
+          <t>50-60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '50-60'}</t>
+          <t>50-60</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'40-50'}</t>
+          <t>40-50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '40-50'}</t>
+          <t>40-50</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'below_40'}</t>
+          <t>below_40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Below 40'}</t>
+          <t>Below 40</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'expired'}</t>
+          <t>expired</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Expired'}</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'renewed'}</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Renewed'}</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'technician_name'}</t>
+          <t>technician_name</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Technician Name'}</t>
+          <t>Technician Name</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'technician_name'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Technician Name'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>technician_signature_choices</t>
+          <t>supervisor_signature_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_applicable'}</t>
+          <t>supervisor_name</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Applicable'}</t>
+          <t>Supervisor Name</t>
         </is>
       </c>
     </row>
@@ -1743,46 +1743,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'supervisor_name'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Supervisor Name'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>supervisor_signature_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'supervisor_name'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Supervisor Name'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>supervisor_signature_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'not_applicable'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Not Applicable'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1794,46 +1794,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'location_1'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Location 1'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>engine_oil_level_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'location_2'}</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Location 2'}</t>
+          <t>1/4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>engine_oil_level_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'location_3'}</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Location 3'}</t>
+          <t>1/2</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1/4'}</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1/4'}</t>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -1862,46 +1862,46 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'1/2'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '1/2'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>engine_oil_level_choices</t>
+          <t>fuel_level_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3/4'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3/4'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>engine_oil_level_choices</t>
+          <t>fuel_level_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'full'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Full'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1913,46 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'good'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fuel_level_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_2,_'label':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': 2, 'label': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fuel_level_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_3,_'label':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
